--- a/bin/Release/Assets/Templates/temp_data.xlsx
+++ b/bin/Release/Assets/Templates/temp_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Συμμετέχων</t>
   </si>
@@ -30,6 +30,15 @@
   </si>
   <si>
     <t>ΔΩΡΟ</t>
+  </si>
+  <si>
+    <t>EUROPHARMACY IKE</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>POWERTECH EARPHONES ME ΘΗΚΗ ΦΟΡΤΙΣΗΣ ΜΑΥΡΟ</t>
   </si>
 </sst>
 </file>
@@ -75,7 +84,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98,6 +107,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/bin/Release/Assets/Templates/temp_data.xlsx
+++ b/bin/Release/Assets/Templates/temp_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Συμμετέχων</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>2310403354</t>
   </si>
   <si>
     <t>POWERTECH EARPHONES ME ΘΗΚΗ ΦΟΡΤΙΣΗΣ ΜΑΥΡΟ</t>
@@ -116,11 +119,11 @@
         <v>7</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2"/>
       <c r="F2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/bin/Release/Assets/Templates/temp_data.xlsx
+++ b/bin/Release/Assets/Templates/temp_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Συμμετέχων</t>
   </si>
@@ -30,18 +30,6 @@
   </si>
   <si>
     <t>ΔΩΡΟ</t>
-  </si>
-  <si>
-    <t>EUROPHARMACY IKE</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2310403354</t>
-  </si>
-  <si>
-    <t>POWERTECH EARPHONES ME ΘΗΚΗ ΦΟΡΤΙΣΗΣ ΜΑΥΡΟ</t>
   </si>
 </sst>
 </file>
@@ -87,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -110,22 +98,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2"/>
-      <c r="B2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2"/>
-      <c r="F2" s="0" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
